--- a/e2e/expectedData/moju_tunjangan_jabatan_2_Q1.xlsx
+++ b/e2e/expectedData/moju_tunjangan_jabatan_2_Q1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="37">
   <si>
     <t>DAFTAR PEMBAYARAN KARYAWAN</t>
   </si>
@@ -92,10 +92,16 @@
     <t>kewajiban pajak 2</t>
   </si>
   <si>
+    <t>1,200.00</t>
+  </si>
+  <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>DILI, 26 Agustus 2026</t>
+    <t>1,290.00</t>
+  </si>
+  <si>
+    <t>DILI, 09 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -615,9 +621,7 @@
       <c r="C7" s="3">
         <v>2352342</v>
       </c>
-      <c r="D7" s="4">
-        <v>100.0</v>
-      </c>
+      <c r="D7" s="4"/>
       <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5">
@@ -630,7 +634,9 @@
       <c r="C8" s="3">
         <v>2123234</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="4">
+        <v>100.0</v>
+      </c>
       <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5">
@@ -643,7 +649,9 @@
       <c r="C9" s="3">
         <v>231234</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4">
+        <v>250.0</v>
+      </c>
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5">
@@ -656,9 +664,7 @@
       <c r="C10" s="3">
         <v>111234232</v>
       </c>
-      <c r="D10" s="4">
-        <v>100.0</v>
-      </c>
+      <c r="D10" s="4"/>
       <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:5">
@@ -671,7 +677,9 @@
       <c r="C11" s="3">
         <v>110928942</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4">
+        <v>100.0</v>
+      </c>
       <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:5">
@@ -684,7 +692,9 @@
       <c r="C12" s="3">
         <v>112344</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4">
+        <v>250.0</v>
+      </c>
       <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:5">
@@ -697,9 +707,7 @@
       <c r="C13" s="3">
         <v>11223342</v>
       </c>
-      <c r="D13" s="4">
-        <v>100.0</v>
-      </c>
+      <c r="D13" s="4"/>
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5">
@@ -712,7 +720,9 @@
       <c r="C14" s="3">
         <v>112344</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="4">
+        <v>100.0</v>
+      </c>
       <c r="E14" s="4"/>
     </row>
     <row r="15" spans="1:5">
@@ -760,7 +770,9 @@
         <v>20</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4">
+        <v>90.0</v>
+      </c>
       <c r="E18" s="4"/>
     </row>
     <row r="19" spans="1:5">
@@ -798,7 +810,9 @@
         <v>1123334</v>
       </c>
       <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
+      <c r="E21" s="4">
+        <v>90.0</v>
+      </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3">
@@ -811,26 +825,26 @@
         <v>12342323</v>
       </c>
       <c r="D22" s="4"/>
-      <c r="E22" s="4">
-        <v>700.0</v>
+      <c r="E22" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
-      <c r="D23" s="6">
-        <v>700.0</v>
-      </c>
-      <c r="E23" s="6">
-        <v>700.0</v>
+      <c r="D23" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B25"/>
       <c r="C25"/>
@@ -839,23 +853,23 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26"/>
       <c r="D26" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E26" s="8"/>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27"/>
       <c r="D27" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E27" s="7"/>
     </row>
@@ -868,23 +882,23 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29"/>
       <c r="D29" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E29" s="7"/>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30"/>
       <c r="D30" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E30" s="7"/>
     </row>

--- a/e2e/expectedData/moju_tunjangan_jabatan_2_Q1.xlsx
+++ b/e2e/expectedData/moju_tunjangan_jabatan_2_Q1.xlsx
@@ -101,7 +101,7 @@
     <t>1,290.00</t>
   </si>
   <si>
-    <t>DILI, 09 September 2026</t>
+    <t>DILI, 10 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
